--- a/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/results/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.023</v>
+        <v>0.227</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006</v>
+        <v>0.022</v>
       </c>
       <c r="E7" t="n">
-        <v>0.017</v>
+        <v>0.205</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.074</v>
+        <v>-0.143</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>-0.044</v>
       </c>
       <c r="E8" t="n">
-        <v>0.034</v>
+        <v>0.09899999999999999</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.024</v>
+        <v>-0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.017</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.392</v>
+        <v>-0.024</v>
       </c>
       <c r="D10" t="n">
-        <v>0.029</v>
+        <v>0.026</v>
       </c>
       <c r="E10" t="n">
-        <v>0.363</v>
+        <v>-0.001999999999999998</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.034</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>-0.008</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.024</v>
+        <v>0.107</v>
       </c>
       <c r="D12" t="n">
-        <v>0.026</v>
+        <v>0.043</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.001999999999999998</v>
+        <v>0.064</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.113</v>
+        <v>0.007</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.051</v>
+        <v>0.024</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06200000000000001</v>
+        <v>-0.017</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.034</v>
+        <v>-0.128</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008</v>
+        <v>0.021</v>
       </c>
       <c r="E14" t="n">
-        <v>0.026</v>
+        <v>0.107</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.054</v>
+        <v>0.005</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.027</v>
+        <v>-0.013</v>
       </c>
       <c r="E15" t="n">
-        <v>0.027</v>
+        <v>-0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0</v>
+        <v>0.032</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.003</v>
+        <v>0.033</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.003</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.046</v>
       </c>
       <c r="D17" t="n">
         <v>-0.002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.012</v>
+        <v>0.044</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.008</v>
+        <v>0.392</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.001</v>
+        <v>0.029</v>
       </c>
       <c r="E18" t="n">
-        <v>0.007</v>
+        <v>0.363</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.143</v>
+        <v>-0.008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.044</v>
+        <v>-0.001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09899999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.401</v>
+        <v>0.197</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.039</v>
+        <v>0.064</v>
       </c>
       <c r="E20" t="n">
-        <v>0.362</v>
+        <v>0.133</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.107</v>
+        <v>-0.074</v>
       </c>
       <c r="D21" t="n">
-        <v>0.043</v>
+        <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>0.064</v>
+        <v>0.034</v>
       </c>
       <c r="F21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.128</v>
+        <v>-0.113</v>
       </c>
       <c r="D22" t="n">
-        <v>0.021</v>
+        <v>-0.051</v>
       </c>
       <c r="E22" t="n">
-        <v>0.107</v>
+        <v>0.06200000000000001</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.022</v>
+        <v>0.023</v>
       </c>
       <c r="D23" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="E23" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.197</v>
+        <v>-0.401</v>
       </c>
       <c r="D24" t="n">
-        <v>0.064</v>
+        <v>-0.039</v>
       </c>
       <c r="E24" t="n">
-        <v>0.133</v>
+        <v>0.362</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.077</v>
+        <v>0.041</v>
       </c>
       <c r="D25" t="n">
-        <v>0.031</v>
+        <v>0.037</v>
       </c>
       <c r="E25" t="n">
-        <v>0.046</v>
+        <v>0.004000000000000004</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.032</v>
+        <v>0.077</v>
       </c>
       <c r="D26" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.001000000000000001</v>
+        <v>0.046</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-0.041</v>
+        <v>-0.066</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.013</v>
+        <v>-0.058</v>
       </c>
       <c r="E27" t="n">
-        <v>0.028</v>
+        <v>0.008</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.041</v>
+        <v>-0.041</v>
       </c>
       <c r="D28" t="n">
-        <v>0.037</v>
+        <v>-0.013</v>
       </c>
       <c r="E28" t="n">
-        <v>0.004000000000000004</v>
+        <v>0.028</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.066</v>
+        <v>0.022</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.058</v>
+        <v>0.015</v>
       </c>
       <c r="E29" t="n">
-        <v>0.008</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.046</v>
+        <v>-0.054</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
       <c r="E30" t="n">
-        <v>0.044</v>
+        <v>0.027</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,16 +1263,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.227</v>
+        <v>-0.019</v>
       </c>
       <c r="D31" t="n">
-        <v>0.022</v>
+        <v>-0.022</v>
       </c>
       <c r="E31" t="n">
-        <v>0.205</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.019</v>
+        <v>-0.014</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.022</v>
+        <v>-0.002</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.005</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.013</v>
+        <v>-0.003</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1430,7 +1430,7 @@
         <v>1.126973544354103</v>
       </c>
       <c r="G2" t="n">
-        <v>1.680728130423187</v>
+        <v>1.680728130423188</v>
       </c>
     </row>
   </sheetData>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.588422507365226</v>
+        <v>1.588422507365227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09950879751532346</v>
+        <v>0.09950879751532972</v>
       </c>
       <c r="D2" t="n">
-        <v>1.393388848090304</v>
+        <v>1.393388848090292</v>
       </c>
       <c r="E2" t="n">
-        <v>1.783456166640149</v>
+        <v>1.783456166640162</v>
       </c>
       <c r="F2" t="n">
-        <v>2.32700165530985e-57</v>
+        <v>2.327001655347131e-57</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002157202703634747</v>
+        <v>0.002157202703634708</v>
       </c>
       <c r="C3" t="n">
         <v>0.02004412832739044</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03712856691954959</v>
+        <v>-0.03712856691954963</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04144297232681908</v>
+        <v>0.04144297232681905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9142950096096352</v>
+        <v>0.9142950096096367</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1541,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02806347567340356</v>
+        <v>-0.02806347567340359</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05180741466195352</v>
+        <v>0.05180741466195353</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1296041425429648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07347719119615768</v>
+        <v>0.07347719119615767</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5880331806434527</v>
+        <v>0.5880331806434524</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002136000897429317</v>
+        <v>0.002136000897429323</v>
       </c>
       <c r="C5" t="n">
         <v>0.03521890701594482</v>
@@ -1575,10 +1575,10 @@
         <v>-0.06689178842868755</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07116379022354617</v>
+        <v>0.0711637902235462</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9516385362649576</v>
+        <v>0.9516385362649575</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1591,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03303202308651738</v>
+        <v>0.03303202308651729</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03286800426819424</v>
+        <v>0.03286800426819425</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0313880815228521</v>
+        <v>-0.03138808152285221</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09745212769588685</v>
+        <v>0.09745212769588679</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3149015555617179</v>
+        <v>0.3149015555617194</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1616,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01521228708610781</v>
+        <v>-0.0152122870861078</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03536389523671276</v>
+        <v>0.03536389523671278</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08452424810311239</v>
+        <v>-0.08452424810311243</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05409967393089678</v>
+        <v>0.05409967393089683</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6670760911481433</v>
+        <v>0.6670760911481435</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1641,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01369113270818713</v>
+        <v>-0.01369113270818714</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03583749565076259</v>
+        <v>0.0358374956507626</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08393133347979262</v>
+        <v>-0.08393133347979266</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05654906806341836</v>
+        <v>0.05654906806341838</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7024363340113149</v>
+        <v>0.7024363340113147</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02619917626172893</v>
+        <v>-0.02619917626172892</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03445373577537432</v>
+        <v>0.03445373577537433</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09372725751432179</v>
+        <v>-0.0937272575143218</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04132890499086392</v>
+        <v>0.04132890499086396</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4470058874486469</v>
+        <v>0.4470058874486471</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.1242064437800987</v>
+        <v>-0.1242064437800989</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05548417525012682</v>
+        <v>0.05548417525012689</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2329534289822559</v>
+        <v>-0.2329534289822562</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01545945857794145</v>
+        <v>-0.01545945857794154</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02518246006139387</v>
+        <v>0.02518246006139378</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1716,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.07320420542333154</v>
+        <v>0.07320420542333134</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05628688228526361</v>
+        <v>0.05628688228526357</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03711605665783071</v>
+        <v>-0.03711605665783083</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1835244675044938</v>
+        <v>0.1835244675044935</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1934107016225535</v>
+        <v>0.1934107016225541</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.06076403853532313</v>
+        <v>-0.06076403853532333</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06002138315034822</v>
+        <v>0.06002138315034827</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1784037878122849</v>
+        <v>-0.1784037878122852</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05687571074163863</v>
+        <v>0.05687571074163852</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3113596568518623</v>
+        <v>0.3113596568518611</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1766,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03935267962244701</v>
+        <v>-0.03935267962244717</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0570298991818517</v>
+        <v>0.05702989918185173</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1511292280608266</v>
+        <v>-0.1511292280608268</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0724238688159326</v>
+        <v>0.07242386881593252</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4901715914374885</v>
+        <v>0.4901715914374869</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08994407386175071</v>
+        <v>-0.08994407386175085</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05595151464980281</v>
+        <v>0.05595151464980278</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1996070274558294</v>
+        <v>-0.1996070274558295</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01971887973232801</v>
+        <v>0.01971887973232782</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1079368395669111</v>
+        <v>0.1079368395669103</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1816,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07972002010245746</v>
+        <v>-0.07972002010245764</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05482862722193878</v>
+        <v>0.05482862722193883</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1871821547792299</v>
+        <v>-0.1871821547792302</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02774211457431494</v>
+        <v>0.02774211457431487</v>
       </c>
       <c r="F15" t="n">
-        <v>0.145950371124213</v>
+        <v>0.1459503711242125</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07580821482423739</v>
+        <v>-0.07580821482423755</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05391836373954736</v>
+        <v>0.05391836373954744</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1814862658590806</v>
+        <v>-0.1814862658590809</v>
       </c>
       <c r="E16" t="n">
         <v>0.02986983621060582</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1597296574439618</v>
+        <v>0.1597296574439616</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.007958708481944419</v>
+        <v>-0.007958708481944608</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05686585901762573</v>
+        <v>0.0568658590176258</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1194137441064231</v>
+        <v>-0.1194137441064234</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1034963271425343</v>
+        <v>0.1034963271425342</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8886948895826481</v>
+        <v>0.8886948895826455</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0267460063729256</v>
+        <v>-0.02674600637292568</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05495082849883492</v>
+        <v>0.05495082849883504</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1344476511512792</v>
+        <v>-0.1344476511512796</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08095563840542805</v>
+        <v>0.08095563840542822</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6264523959201854</v>
+        <v>0.6264523959201853</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1916,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08417048724369847</v>
+        <v>-0.08417048724369865</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05356575306273113</v>
+        <v>0.05356575306273122</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1891574340514176</v>
+        <v>-0.1891574340514179</v>
       </c>
       <c r="E19" t="n">
         <v>0.02081645956402065</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1161016281223222</v>
+        <v>0.1161016281223219</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1941,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1315545875635714</v>
+        <v>-0.1315545875635716</v>
       </c>
       <c r="C20" t="n">
         <v>0.05402663862558477</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2374448534754782</v>
+        <v>-0.2374448534754783</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02566432165166473</v>
+        <v>-0.02566432165166485</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01489200108264323</v>
+        <v>0.01489200108264313</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1966,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1243413906692294</v>
+        <v>-0.1243413906692296</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05618303846984329</v>
+        <v>0.0561830384698433</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2344581226121506</v>
+        <v>-0.2344581226121508</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01422465872630824</v>
+        <v>-0.01422465872630838</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02688742972151429</v>
+        <v>0.02688742972151414</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1991,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07290986245855961</v>
+        <v>-0.07290986245855967</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05651076265826965</v>
+        <v>0.05651076265826972</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1836689220076591</v>
+        <v>-0.1836689220076593</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03784919709053985</v>
+        <v>0.03784919709053994</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1969832133925167</v>
+        <v>0.1969832133925169</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -2016,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01550122276689218</v>
+        <v>-0.01550122276689234</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05392880208198828</v>
+        <v>0.05392880208198836</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1211997325769779</v>
+        <v>-0.1211997325769782</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09019728704319352</v>
+        <v>0.09019728704319353</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7737764608404225</v>
+        <v>0.7737764608404205</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01736702286559946</v>
+        <v>-0.01736702286559949</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04895754327588756</v>
+        <v>0.04895754327588753</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1133220444579002</v>
+        <v>-0.1133220444579001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07858799872670125</v>
+        <v>0.07858799872670116</v>
       </c>
       <c r="F24" t="n">
-        <v>0.722787075588748</v>
+        <v>0.7227870755887473</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2069,16 +2069,16 @@
         <v>0.01900414985650927</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0256228364739088</v>
+        <v>0.02562283647390875</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03121568681411126</v>
+        <v>-0.03121568681411115</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0692239865271298</v>
+        <v>0.06922398652712969</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4582764034316499</v>
+        <v>0.458276403431649</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2091,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0113651123997222</v>
+        <v>-0.01136511239972217</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03076545132329944</v>
+        <v>0.03076545132329943</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07166428896150925</v>
+        <v>-0.07166428896150918</v>
       </c>
       <c r="E26" t="n">
         <v>0.04893406416206485</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7118210062148224</v>
+        <v>0.7118210062148231</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2116,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008288872114818002</v>
+        <v>0.008288872114818061</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03118021288371119</v>
+        <v>0.03118021288371117</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0528232221675477</v>
+        <v>-0.0528232221675476</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06940096639718371</v>
+        <v>0.06940096639718372</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7903643050508866</v>
+        <v>0.790364305050885</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2141,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.04441792109265481</v>
+        <v>0.04441792109265486</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0314722530820989</v>
+        <v>0.03147225308209888</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.01726656146058875</v>
+        <v>-0.01726656146058866</v>
       </c>
       <c r="E28" t="n">
         <v>0.1061024036458984</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1581455893971984</v>
+        <v>0.1581455893971977</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0111102689020691</v>
+        <v>-0.01111026890206905</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03230457849540543</v>
+        <v>0.03230457849540542</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07442607928881088</v>
+        <v>-0.0744260792888108</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05220554148467267</v>
+        <v>0.0522055414846727</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7309046284390847</v>
+        <v>0.7309046284390859</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2194,16 +2194,16 @@
         <v>0.2303472064753823</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04274619914367982</v>
+        <v>0.04274619914367981</v>
       </c>
       <c r="D30" t="n">
-        <v>0.146566195677793</v>
+        <v>0.1465661956777929</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3141282172729717</v>
+        <v>0.3141282172729716</v>
       </c>
       <c r="F30" t="n">
-        <v>7.096210791271728e-08</v>
+        <v>7.096210791271779e-08</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2212,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4907763416057432</v>
+        <v>-0.001023762880892497</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01020349621388546</v>
+        <v>0.001412550988754019</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4707778565101369</v>
+        <v>-0.003792311945176817</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5107748267013495</v>
+        <v>0.001744786183391824</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.4685982250511583</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2241,19 +2241,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0008847896531368721</v>
+        <v>-0.0008847896531368739</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001755881165775747</v>
+        <v>0.001755881165775725</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.00432625349918954</v>
+        <v>-0.004326253499189499</v>
       </c>
       <c r="E32" t="n">
-        <v>0.002556674192915796</v>
+        <v>0.002556674192915751</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6143311968318158</v>
+        <v>0.6143311968318106</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.007684909964816857</v>
+        <v>-0.007684909964816858</v>
       </c>
       <c r="C33" t="n">
-        <v>0.004562970024586861</v>
+        <v>0.004562970024586866</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.01662816687554295</v>
+        <v>-0.01662816687554296</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001258346945909235</v>
+        <v>0.001258346945909245</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09214489260396617</v>
+        <v>0.09214489260396649</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2287,23 +2287,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001323773742398877</v>
+        <v>0.009295972736054448</v>
       </c>
       <c r="C34" t="n">
-        <v>0.001449666664927172</v>
+        <v>0.02351946149446093</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.001517520710446674</v>
+        <v>-0.03680132472886557</v>
       </c>
       <c r="E34" t="n">
-        <v>0.004165068195244429</v>
+        <v>0.05539327020097446</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3611598015227339</v>
+        <v>0.692661358138289</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2312,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.009295972736054538</v>
+        <v>0.4907763416057432</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02351946149446092</v>
+        <v>0.01020349621388547</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03680132472886546</v>
+        <v>0.4707778565101369</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05539327020097454</v>
+        <v>0.5107748267013495</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6926613581382861</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2337,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.001023762880892494</v>
+        <v>0.001323773742398876</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001412550988754018</v>
+        <v>0.001449666664927172</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.003792311945176812</v>
+        <v>-0.001517520710446677</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001744786183391824</v>
+        <v>0.004165068195244427</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4685982250511591</v>
+        <v>0.3611598015227346</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2405,10 +2405,10 @@
         <v>-2.820303044554361</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5099234395092674</v>
+        <v>0.509923439509295</v>
       </c>
       <c r="D2" t="n">
-        <v>3.187077352403665e-08</v>
+        <v>3.187077352409087e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2418,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02464939576457219</v>
+        <v>-0.02464939576457213</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1003099681595393</v>
+        <v>0.1003099681595394</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8058894933269592</v>
+        <v>0.8058894933269598</v>
       </c>
     </row>
     <row r="4">
@@ -2434,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2249663577428584</v>
+        <v>0.2249663577428586</v>
       </c>
       <c r="C4" t="n">
         <v>0.2337176582603367</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3357703370011803</v>
+        <v>0.3357703370011802</v>
       </c>
     </row>
     <row r="5">
@@ -2450,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.819137367488546</v>
+        <v>0.8191373674885462</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734167828528216</v>
+        <v>0.1734167828528217</v>
       </c>
       <c r="D5" t="n">
-        <v>2.317989576597463e-06</v>
+        <v>2.317989576597488e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2466,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03652125765996359</v>
+        <v>0.0365212576599634</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1917132959179622</v>
+        <v>0.1917132959179624</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8489178549322626</v>
+        <v>0.8489178549322635</v>
       </c>
     </row>
     <row r="7">
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2789564326928404</v>
+        <v>0.2789564326928405</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901139906226966</v>
+        <v>0.1901139906226967</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1422913540098488</v>
+        <v>0.1422913540098489</v>
       </c>
     </row>
     <row r="8">
@@ -2501,10 +2501,10 @@
         <v>0.1068531552827688</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1953287956048304</v>
+        <v>0.1953287956048305</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5843495250374455</v>
+        <v>0.5843495250374457</v>
       </c>
     </row>
     <row r="9">
@@ -2514,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8765772051307453</v>
+        <v>0.8765772051307454</v>
       </c>
       <c r="C9" t="n">
         <v>0.1697332036095896</v>
       </c>
       <c r="D9" t="n">
-        <v>2.411578475116389e-07</v>
+        <v>2.411578475116398e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2530,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04447986866030706</v>
+        <v>-0.04447986866030648</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604513322559265</v>
+        <v>0.260451332255926</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8643967854929899</v>
+        <v>0.8643967854929914</v>
       </c>
     </row>
     <row r="11">
@@ -2549,10 +2549,10 @@
         <v>-0.2727472209256582</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2791278961561443</v>
+        <v>0.2791278961561445</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3284995130487423</v>
+        <v>0.3284995130487426</v>
       </c>
     </row>
     <row r="12">
@@ -2562,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.07889678868393109</v>
+        <v>0.07889678868393121</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596148796948626</v>
+        <v>0.2596148796948629</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7612045862333772</v>
+        <v>0.7612045862333771</v>
       </c>
     </row>
     <row r="13">
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04019393041481655</v>
+        <v>0.0401939304148166</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2574204041328305</v>
+        <v>0.2574204041328301</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8759217249006986</v>
+        <v>0.8759217249006983</v>
       </c>
     </row>
     <row r="14">
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.04910228165084237</v>
+        <v>-0.04910228165084263</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2612561015991027</v>
+        <v>0.2612561015991028</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8509182551619328</v>
+        <v>0.8509182551619321</v>
       </c>
     </row>
     <row r="15">
@@ -2613,10 +2613,10 @@
         <v>0.1160743543422993</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2571236264961846</v>
+        <v>0.2571236264961845</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6516767631412981</v>
+        <v>0.6516767631412977</v>
       </c>
     </row>
     <row r="16">
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.00251242103022585</v>
+        <v>-0.002512421030225608</v>
       </c>
       <c r="C16" t="n">
-        <v>0.238607871750487</v>
+        <v>0.2386078717504875</v>
       </c>
       <c r="D16" t="n">
-        <v>0.991598831614466</v>
+        <v>0.9915988316144669</v>
       </c>
     </row>
     <row r="17">
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1088094847883378</v>
+        <v>0.1088094847883379</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2546184298925978</v>
+        <v>0.2546184298925979</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6691292855457313</v>
+        <v>0.6691292855457309</v>
       </c>
     </row>
     <row r="18">
@@ -2658,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1371054629493658</v>
+        <v>-0.1371054629493655</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2637238215346596</v>
+        <v>0.2637238215346593</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6031453060320007</v>
+        <v>0.6031453060320012</v>
       </c>
     </row>
     <row r="19">
@@ -2674,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02469784288290733</v>
+        <v>-0.02469784288290731</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2529058254775154</v>
+        <v>0.2529058254775156</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9222052306173942</v>
+        <v>0.9222052306173943</v>
       </c>
     </row>
     <row r="20">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.06845683158478727</v>
+        <v>-0.06845683158478705</v>
       </c>
       <c r="C20" t="n">
         <v>0.2673011584514005</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7978707191500399</v>
+        <v>0.7978707191500406</v>
       </c>
     </row>
     <row r="21">
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2086621675742924</v>
+        <v>0.2086621675742927</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244281566241917</v>
+        <v>0.2442815662419177</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3930013184626148</v>
+        <v>0.3930013184626154</v>
       </c>
     </row>
     <row r="22">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.175406708188101</v>
+        <v>-0.1754067081881009</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2700541998112385</v>
+        <v>0.2700541998112387</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5159996811704789</v>
+        <v>0.5159996811704795</v>
       </c>
     </row>
     <row r="23">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.500438422493073</v>
+        <v>-0.5004384224930729</v>
       </c>
       <c r="C23" t="n">
         <v>0.2870894861894648</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08130839926920316</v>
+        <v>0.08130839926920327</v>
       </c>
     </row>
     <row r="24">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9379041483579632</v>
+        <v>0.9379041483579631</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1484949273354128</v>
+        <v>0.1484949273354127</v>
       </c>
       <c r="D24" t="n">
-        <v>2.683009814405812e-10</v>
+        <v>2.683009814405772e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776000776467407</v>
+        <v>-0.5776000776467408</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143336799033598</v>
+        <v>0.1143336799033597</v>
       </c>
       <c r="D25" t="n">
-        <v>4.374815955439421e-07</v>
+        <v>4.37481595543926e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.235745269551033</v>
+        <v>0.2357452695510329</v>
       </c>
       <c r="C26" t="n">
         <v>0.1505208025229895</v>
@@ -2802,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04479861183336146</v>
+        <v>-0.04479861183336142</v>
       </c>
       <c r="C27" t="n">
         <v>0.1611783258696416</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7810550458340705</v>
+        <v>0.7810550458340706</v>
       </c>
     </row>
     <row r="28">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0752872762537825</v>
+        <v>-0.07528727625378238</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1614983128820299</v>
+        <v>0.1614983128820298</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6410866959853154</v>
+        <v>0.6410866959853159</v>
       </c>
     </row>
     <row r="29">
@@ -2834,29 +2834,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09387617646092151</v>
+        <v>0.09387617646092163</v>
       </c>
       <c r="C29" t="n">
         <v>0.1543340718197335</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5430110331238934</v>
+        <v>0.5430110331238927</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.04715208655231701</v>
+        <v>-0.002469929930368318</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04889616403699378</v>
+        <v>0.007130763690581516</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3348800057442065</v>
+        <v>0.729059682342319</v>
       </c>
     </row>
     <row r="31">
@@ -2866,13 +2866,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004826402612991665</v>
+        <v>-0.004826402612991674</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008314480096143126</v>
+        <v>0.008314480096143233</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5615898992578215</v>
+        <v>0.5615898992578258</v>
       </c>
     </row>
     <row r="32">
@@ -2882,61 +2882,61 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.003793322855986097</v>
+        <v>-0.003793322855986095</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0222320269000005</v>
+        <v>0.02223202690000069</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8645192309060565</v>
+        <v>0.8645192309060578</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.006311908087997965</v>
+        <v>0.2256479096144981</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006867343796543262</v>
+        <v>0.1147189874002693</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3580331856516404</v>
+        <v>0.04918757099961338</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.2256479096144981</v>
+        <v>0.04715208655231709</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1147189874002692</v>
+        <v>0.04889616403699421</v>
       </c>
       <c r="D34" t="n">
-        <v>0.04918757099961327</v>
+        <v>0.33488000574421</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.002469929930368324</v>
+        <v>0.006311908087997961</v>
       </c>
       <c r="C35" t="n">
-        <v>0.00713076369058151</v>
+        <v>0.006867343796543269</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7290596823423182</v>
+        <v>0.3580331856516412</v>
       </c>
     </row>
   </sheetData>
